--- a/groups/dm-with-raeleen/drafts/DTET-Estimate-June2026.xlsx
+++ b/groups/dm-with-raeleen/drafts/DTET-Estimate-June2026.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Estimate" sheetId="1" r:id="rId1"/>
+    <sheet name="Rates &amp; Settings" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -397,29 +398,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:O93"/>
   <cols>
-    <col min="1" max="1" width="4.83203125" customWidth="1"/>
-    <col min="2" max="2" width="60.83203125" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="65.83203125" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" customWidth="1"/>
-    <col min="9" max="9" width="8.83203125" customWidth="1"/>
-    <col min="10" max="10" width="8.83203125" customWidth="1"/>
-    <col min="11" max="11" width="8.83203125" customWidth="1"/>
-    <col min="12" max="12" width="8.83203125" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="6.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="6.83203125" customWidth="1"/>
+    <col min="8" max="8" width="22.83203125" customWidth="1"/>
+    <col min="9" max="9" width="6.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="26.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v/>
+        <v>Mettro Estimate Builder</v>
       </c>
       <c r="B1" t="str">
-        <v>ESTIMATE DETAILS</v>
+        <v/>
       </c>
       <c r="C1" t="str">
         <v/>
@@ -452,6 +452,12 @@
         <v/>
       </c>
       <c r="M1" t="str">
+        <v/>
+      </c>
+      <c r="N1" t="str">
+        <v/>
+      </c>
+      <c r="O1" t="str">
         <v/>
       </c>
     </row>
@@ -460,13 +466,13 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>Hours estimate</v>
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>Estimate ($)</v>
+        <v/>
       </c>
       <c r="D2" t="str">
-        <v>Costing makeup (hrs)</v>
+        <v/>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -493,15 +499,21 @@
         <v/>
       </c>
       <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v/>
+        <v>Client</v>
       </c>
       <c r="B3" t="str">
-        <v/>
+        <v>DTET (Department of Trade, Employment and Training)</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -513,16 +525,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
+        <v>GST %</v>
+      </c>
+      <c r="G3">
+        <v>0.1</v>
       </c>
       <c r="H3" t="str">
         <v/>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>Live quote summary</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -534,12 +546,18 @@
         <v/>
       </c>
       <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v/>
+        <v>Project</v>
       </c>
       <c r="B4" t="str">
         <v>DTET High Performance Website, Phase 1</v>
@@ -551,39 +569,45 @@
         <v/>
       </c>
       <c r="E4" t="str">
-        <v>STRAT</v>
+        <v/>
       </c>
       <c r="F4" t="str">
-        <v>DESIGN</v>
-      </c>
-      <c r="G4" t="str">
-        <v>DEV</v>
+        <v>Contingency %</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
       </c>
       <c r="H4" t="str">
-        <v>QA</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>CONTENT</v>
+        <v>Labour &amp; materials</v>
       </c>
       <c r="J4" t="str">
-        <v>SUPPORT</v>
-      </c>
-      <c r="K4" t="str">
-        <v>PM</v>
+        <v/>
+      </c>
+      <c r="K4">
+        <v>54040</v>
       </c>
       <c r="L4" t="str">
-        <v>OTHER</v>
+        <v/>
       </c>
       <c r="M4" t="str">
-        <v>TOTAL inc markup/profit</v>
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v/>
+        <v>Prepared by</v>
       </c>
       <c r="B5" t="str">
-        <v/>
+        <v>Mettro Digital</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -595,27 +619,33 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
+        <v>Discount %</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
       </c>
       <c r="H5" t="str">
         <v/>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>Contingency</v>
       </c>
       <c r="J5" t="str">
         <v/>
       </c>
-      <c r="K5" t="str">
-        <v/>
+      <c r="K5">
+        <v>0</v>
       </c>
       <c r="L5" t="str">
         <v/>
       </c>
       <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
         <v/>
       </c>
     </row>
@@ -645,18 +675,24 @@
         <v/>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>Discount</v>
       </c>
       <c r="J6" t="str">
         <v/>
       </c>
-      <c r="K6" t="str">
-        <v/>
+      <c r="K6">
+        <v>0</v>
       </c>
       <c r="L6" t="str">
         <v/>
       </c>
       <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
         <v/>
       </c>
     </row>
@@ -671,33 +707,39 @@
         <v/>
       </c>
       <c r="D7" t="str">
-        <v>RATE</v>
-      </c>
-      <c r="E7">
-        <v>250</v>
-      </c>
-      <c r="F7">
-        <v>180</v>
-      </c>
-      <c r="G7">
-        <v>230</v>
-      </c>
-      <c r="H7">
-        <v>230</v>
-      </c>
-      <c r="I7">
-        <v>180</v>
-      </c>
-      <c r="J7">
-        <v>190</v>
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>Subtotal</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
       </c>
       <c r="K7">
-        <v>190</v>
-      </c>
-      <c r="L7">
-        <v>350</v>
+        <v>54040</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
       </c>
       <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
         <v/>
       </c>
     </row>
@@ -727,13 +769,13 @@
         <v/>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>Total inc GST</v>
       </c>
       <c r="J8" t="str">
         <v/>
       </c>
-      <c r="K8" t="str">
-        <v/>
+      <c r="K8">
+        <v>59444</v>
       </c>
       <c r="L8" t="str">
         <v/>
@@ -741,22 +783,28 @@
       <c r="M8" t="str">
         <v/>
       </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>1</v>
+      <c r="A9" t="str">
+        <v/>
       </c>
       <c r="B9" t="str">
-        <v>Blueprint Strategy</v>
-      </c>
-      <c r="C9">
-        <v>8650</v>
-      </c>
-      <c r="D9">
-        <v>37</v>
-      </c>
-      <c r="E9">
-        <v>27</v>
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -773,55 +821,67 @@
       <c r="J9" t="str">
         <v/>
       </c>
-      <c r="K9">
-        <v>10</v>
+      <c r="K9" t="str">
+        <v/>
       </c>
       <c r="L9" t="str">
         <v/>
       </c>
       <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v/>
+        <v>Type</v>
       </c>
       <c r="B10" t="str">
-        <v>Project setup, brief documents, schedule, client material requests</v>
+        <v>Scope / inclusion</v>
       </c>
       <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10">
-        <v>3</v>
+        <v>Price</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Role 1</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>Hrs</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>Role 2</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>Hrs</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Role 3</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>Hrs</v>
       </c>
       <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10">
-        <v>3</v>
+        <v>Material cost</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Line total</v>
       </c>
       <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10">
-        <v>570</v>
+        <v>Section key</v>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -829,16 +889,16 @@
         <v/>
       </c>
       <c r="B11" t="str">
-        <v>Project kickoff x 2 team members</v>
+        <v/>
       </c>
       <c r="C11" t="str">
         <v/>
       </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -855,31 +915,37 @@
       <c r="J11" t="str">
         <v/>
       </c>
-      <c r="K11">
-        <v>1</v>
+      <c r="K11" t="str">
+        <v/>
       </c>
       <c r="L11" t="str">
         <v/>
       </c>
-      <c r="M11">
-        <v>440</v>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
+        <v>Header</v>
       </c>
       <c r="B12" t="str">
-        <v>Review existing DTET site content and assets</v>
-      </c>
-      <c r="C12" t="str">
-        <v/>
-      </c>
-      <c r="D12">
-        <v>2</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
+        <v>Blueprint Strategy</v>
+      </c>
+      <c r="C12">
+        <v>9390</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -900,27 +966,33 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v/>
-      </c>
-      <c r="M12">
-        <v>500</v>
+        <v>Blueprint Strategy</v>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B13" t="str">
-        <v>Strategy workshops, user journeys, UI/UX, content types, taxonomy, filtering and site structure</v>
+        <v>Project setup, brief documents, schedule, client material requests</v>
       </c>
       <c r="C13" t="str">
         <v/>
       </c>
-      <c r="D13">
-        <v>14</v>
+      <c r="D13" t="str">
+        <v>Project Management</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -938,36 +1010,42 @@
         <v/>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>630</v>
       </c>
       <c r="L13" t="str">
-        <v/>
-      </c>
-      <c r="M13">
-        <v>3200</v>
+        <v>Blueprint Strategy</v>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B14" t="str">
-        <v>User journey and taxonomy analysis</v>
+        <v>Project kickoff x 2 team members</v>
       </c>
       <c r="C14" t="str">
         <v/>
       </c>
-      <c r="D14">
-        <v>4</v>
+      <c r="D14" t="str">
+        <v>Strategy</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
+        <v>Project Management</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -978,31 +1056,37 @@
       <c r="J14" t="str">
         <v/>
       </c>
-      <c r="K14" t="str">
-        <v/>
+      <c r="K14">
+        <v>480</v>
       </c>
       <c r="L14" t="str">
-        <v/>
-      </c>
-      <c r="M14">
-        <v>1000</v>
+        <v>Blueprint Strategy</v>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B15" t="str">
-        <v>Technical framework and plugin recommendations</v>
+        <v>Review existing DTET site content and assets</v>
       </c>
       <c r="C15" t="str">
         <v/>
       </c>
-      <c r="D15">
-        <v>3</v>
+      <c r="D15" t="str">
+        <v>Strategy</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -1019,37 +1103,43 @@
       <c r="J15" t="str">
         <v/>
       </c>
-      <c r="K15" t="str">
-        <v/>
+      <c r="K15">
+        <v>540</v>
       </c>
       <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15">
-        <v>750</v>
+        <v>Blueprint Strategy</v>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B16" t="str">
-        <v>Blueprint strategy document</v>
+        <v>Strategy workshops, user journeys, UI/UX, content types, taxonomy, filtering and site structure</v>
       </c>
       <c r="C16" t="str">
         <v/>
       </c>
-      <c r="D16">
-        <v>8</v>
+      <c r="D16" t="str">
+        <v>Strategy</v>
       </c>
       <c r="E16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
+        <v>Project Management</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -1060,31 +1150,37 @@
       <c r="J16" t="str">
         <v/>
       </c>
-      <c r="K16" t="str">
-        <v/>
+      <c r="K16">
+        <v>3480</v>
       </c>
       <c r="L16" t="str">
-        <v/>
-      </c>
-      <c r="M16">
-        <v>2000</v>
+        <v>Blueprint Strategy</v>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B17" t="str">
-        <v>Client sign-off and approval</v>
+        <v>User journey and taxonomy analysis</v>
       </c>
       <c r="C17" t="str">
         <v/>
       </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="str">
-        <v/>
+      <c r="D17" t="str">
+        <v>Strategy</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
       </c>
       <c r="F17" t="str">
         <v/>
@@ -1102,30 +1198,36 @@
         <v/>
       </c>
       <c r="K17">
-        <v>1</v>
+        <v>1080</v>
       </c>
       <c r="L17" t="str">
-        <v/>
-      </c>
-      <c r="M17">
-        <v>190</v>
+        <v>Blueprint Strategy</v>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B18" t="str">
-        <v/>
+        <v>Technical framework and plugin recommendations</v>
       </c>
       <c r="C18" t="str">
         <v/>
       </c>
       <c r="D18" t="str">
-        <v/>
-      </c>
-      <c r="E18" t="str">
-        <v/>
+        <v>Strategy</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -1142,34 +1244,40 @@
       <c r="J18" t="str">
         <v/>
       </c>
-      <c r="K18" t="str">
-        <v/>
+      <c r="K18">
+        <v>810</v>
       </c>
       <c r="L18" t="str">
-        <v/>
+        <v>Blueprint Strategy</v>
       </c>
       <c r="M18" t="str">
         <v/>
       </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>2</v>
+      <c r="A19" t="str">
+        <v>Item</v>
       </c>
       <c r="B19" t="str">
-        <v>Design</v>
-      </c>
-      <c r="C19">
-        <v>8850</v>
-      </c>
-      <c r="D19">
-        <v>49</v>
-      </c>
-      <c r="E19" t="str">
-        <v/>
-      </c>
-      <c r="F19">
-        <v>46</v>
+        <v>Blueprint strategy document</v>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v>Strategy</v>
+      </c>
+      <c r="E19">
+        <v>8</v>
+      </c>
+      <c r="F19" t="str">
+        <v/>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1184,33 +1292,39 @@
         <v/>
       </c>
       <c r="K19">
-        <v>3</v>
+        <v>2160</v>
       </c>
       <c r="L19" t="str">
-        <v/>
+        <v>Blueprint Strategy</v>
       </c>
       <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B20" t="str">
-        <v>Homepage and one internal page, initial concept design</v>
+        <v>Client sign-off and approval</v>
       </c>
       <c r="C20" t="str">
         <v/>
       </c>
-      <c r="D20">
-        <v>10</v>
-      </c>
-      <c r="E20" t="str">
-        <v/>
-      </c>
-      <c r="F20">
-        <v>10</v>
+      <c r="D20" t="str">
+        <v>Project Management</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1224,34 +1338,40 @@
       <c r="J20" t="str">
         <v/>
       </c>
-      <c r="K20" t="str">
-        <v/>
+      <c r="K20">
+        <v>210</v>
       </c>
       <c r="L20" t="str">
-        <v/>
-      </c>
-      <c r="M20">
-        <v>1800</v>
+        <v>Blueprint Strategy</v>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v/>
+        <v>Spacer</v>
       </c>
       <c r="B21" t="str">
-        <v>Login / authentication screen</v>
+        <v/>
       </c>
       <c r="C21" t="str">
         <v/>
       </c>
-      <c r="D21">
-        <v>1</v>
+      <c r="D21" t="str">
+        <v/>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
-      <c r="F21">
-        <v>1</v>
+      <c r="F21" t="str">
+        <v/>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1271,28 +1391,34 @@
       <c r="L21" t="str">
         <v/>
       </c>
-      <c r="M21">
-        <v>180</v>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v/>
+        <v>Header</v>
       </c>
       <c r="B22" t="str">
-        <v>Journey home page design</v>
-      </c>
-      <c r="C22" t="str">
-        <v/>
-      </c>
-      <c r="D22">
-        <v>4</v>
+        <v>Design</v>
+      </c>
+      <c r="C22">
+        <v>10290</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
-      <c r="F22">
-        <v>4</v>
+      <c r="F22" t="str">
+        <v/>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1310,30 +1436,36 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v/>
-      </c>
-      <c r="M22">
-        <v>720</v>
+        <v>Design</v>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B23" t="str">
-        <v>Resource library view, 2 layout options</v>
+        <v>Homepage and one internal page, initial concept design</v>
       </c>
       <c r="C23" t="str">
         <v/>
       </c>
-      <c r="D23">
-        <v>6</v>
-      </c>
-      <c r="E23" t="str">
-        <v/>
-      </c>
-      <c r="F23">
-        <v>6</v>
+      <c r="D23" t="str">
+        <v>Design</v>
+      </c>
+      <c r="E23">
+        <v>10</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1347,34 +1479,40 @@
       <c r="J23" t="str">
         <v/>
       </c>
-      <c r="K23" t="str">
-        <v/>
+      <c r="K23">
+        <v>2100</v>
       </c>
       <c r="L23" t="str">
-        <v/>
-      </c>
-      <c r="M23">
-        <v>1080</v>
+        <v>Design</v>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B24" t="str">
-        <v>Resource detail view</v>
+        <v>Login / authentication screen</v>
       </c>
       <c r="C24" t="str">
         <v/>
       </c>
-      <c r="D24">
-        <v>4</v>
-      </c>
-      <c r="E24" t="str">
-        <v/>
-      </c>
-      <c r="F24">
-        <v>4</v>
+      <c r="D24" t="str">
+        <v>Design</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1388,34 +1526,40 @@
       <c r="J24" t="str">
         <v/>
       </c>
-      <c r="K24" t="str">
-        <v/>
+      <c r="K24">
+        <v>210</v>
       </c>
       <c r="L24" t="str">
-        <v/>
-      </c>
-      <c r="M24">
-        <v>720</v>
+        <v>Design</v>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B25" t="str">
-        <v>Standard pages x 2</v>
+        <v>Taxonomy landing page design</v>
       </c>
       <c r="C25" t="str">
         <v/>
       </c>
-      <c r="D25">
-        <v>3</v>
-      </c>
-      <c r="E25" t="str">
-        <v/>
-      </c>
-      <c r="F25">
-        <v>3</v>
+      <c r="D25" t="str">
+        <v>Design</v>
+      </c>
+      <c r="E25">
+        <v>4</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1429,34 +1573,40 @@
       <c r="J25" t="str">
         <v/>
       </c>
-      <c r="K25" t="str">
-        <v/>
+      <c r="K25">
+        <v>840</v>
       </c>
       <c r="L25" t="str">
-        <v/>
-      </c>
-      <c r="M25">
-        <v>540</v>
+        <v>Design</v>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B26" t="str">
-        <v>Content format display design (video, PDF, article, tool)</v>
+        <v>Resource library view, 2 layout options</v>
       </c>
       <c r="C26" t="str">
         <v/>
       </c>
-      <c r="D26">
-        <v>3</v>
-      </c>
-      <c r="E26" t="str">
-        <v/>
-      </c>
-      <c r="F26">
-        <v>3</v>
+      <c r="D26" t="str">
+        <v>Design</v>
+      </c>
+      <c r="E26">
+        <v>6</v>
+      </c>
+      <c r="F26" t="str">
+        <v/>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1470,34 +1620,40 @@
       <c r="J26" t="str">
         <v/>
       </c>
-      <c r="K26" t="str">
-        <v/>
+      <c r="K26">
+        <v>1260</v>
       </c>
       <c r="L26" t="str">
-        <v/>
-      </c>
-      <c r="M26">
-        <v>540</v>
+        <v>Design</v>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B27" t="str">
-        <v>Design system setup, colour palette, typography, buttons and components</v>
+        <v>Resource detail view</v>
       </c>
       <c r="C27" t="str">
         <v/>
       </c>
-      <c r="D27">
-        <v>6</v>
-      </c>
-      <c r="E27" t="str">
-        <v/>
-      </c>
-      <c r="F27">
-        <v>6</v>
+      <c r="D27" t="str">
+        <v>Design</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
+      <c r="F27" t="str">
+        <v/>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1511,34 +1667,40 @@
       <c r="J27" t="str">
         <v/>
       </c>
-      <c r="K27" t="str">
-        <v/>
+      <c r="K27">
+        <v>840</v>
       </c>
       <c r="L27" t="str">
-        <v/>
-      </c>
-      <c r="M27">
-        <v>1080</v>
+        <v>Design</v>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B28" t="str">
-        <v>Responsive layouts across key templates (mobile, tablet, desktop)</v>
+        <v>Standard pages x 2</v>
       </c>
       <c r="C28" t="str">
         <v/>
       </c>
-      <c r="D28">
+      <c r="D28" t="str">
+        <v>Design</v>
+      </c>
+      <c r="E28">
         <v>3</v>
       </c>
-      <c r="E28" t="str">
-        <v/>
-      </c>
-      <c r="F28">
-        <v>3</v>
+      <c r="F28" t="str">
+        <v/>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1552,34 +1714,40 @@
       <c r="J28" t="str">
         <v/>
       </c>
-      <c r="K28" t="str">
-        <v/>
+      <c r="K28">
+        <v>630</v>
       </c>
       <c r="L28" t="str">
-        <v/>
-      </c>
-      <c r="M28">
-        <v>540</v>
+        <v>Design</v>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B29" t="str">
-        <v>WCAG AA design review across all templates</v>
+        <v>Content format display design (video, PDF, article, tool)</v>
       </c>
       <c r="C29" t="str">
         <v/>
       </c>
-      <c r="D29">
-        <v>2</v>
-      </c>
-      <c r="E29" t="str">
-        <v/>
-      </c>
-      <c r="F29">
-        <v>2</v>
+      <c r="D29" t="str">
+        <v>Design</v>
+      </c>
+      <c r="E29">
+        <v>3</v>
+      </c>
+      <c r="F29" t="str">
+        <v/>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1593,34 +1761,40 @@
       <c r="J29" t="str">
         <v/>
       </c>
-      <c r="K29" t="str">
-        <v/>
+      <c r="K29">
+        <v>630</v>
       </c>
       <c r="L29" t="str">
-        <v/>
-      </c>
-      <c r="M29">
-        <v>360</v>
+        <v>Design</v>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B30" t="str">
-        <v>Two rounds of design feedback</v>
+        <v>Design system setup, colour palette, typography, buttons and components</v>
       </c>
       <c r="C30" t="str">
         <v/>
       </c>
-      <c r="D30">
+      <c r="D30" t="str">
+        <v>Design</v>
+      </c>
+      <c r="E30">
         <v>6</v>
       </c>
-      <c r="E30" t="str">
-        <v/>
-      </c>
-      <c r="F30">
-        <v>4</v>
+      <c r="F30" t="str">
+        <v/>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1635,30 +1809,36 @@
         <v/>
       </c>
       <c r="K30">
-        <v>2</v>
+        <v>1260</v>
       </c>
       <c r="L30" t="str">
-        <v/>
-      </c>
-      <c r="M30">
-        <v>1100</v>
+        <v>Design</v>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B31" t="str">
-        <v>Client sign-off and approval</v>
+        <v>Responsive layouts across key templates (mobile, tablet, desktop)</v>
       </c>
       <c r="C31" t="str">
         <v/>
       </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
-      <c r="E31" t="str">
-        <v/>
+      <c r="D31" t="str">
+        <v>Design</v>
+      </c>
+      <c r="E31">
+        <v>3</v>
       </c>
       <c r="F31" t="str">
         <v/>
@@ -1676,30 +1856,36 @@
         <v/>
       </c>
       <c r="K31">
-        <v>1</v>
+        <v>630</v>
       </c>
       <c r="L31" t="str">
-        <v/>
-      </c>
-      <c r="M31">
-        <v>190</v>
+        <v>Design</v>
+      </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>WCAG AA design review across all templates</v>
       </c>
       <c r="C32" t="str">
         <v/>
       </c>
       <c r="D32" t="str">
-        <v/>
-      </c>
-      <c r="E32" t="str">
-        <v/>
+        <v>Design</v>
+      </c>
+      <c r="E32">
+        <v>2</v>
       </c>
       <c r="F32" t="str">
         <v/>
@@ -1716,37 +1902,43 @@
       <c r="J32" t="str">
         <v/>
       </c>
-      <c r="K32" t="str">
-        <v/>
+      <c r="K32">
+        <v>420</v>
       </c>
       <c r="L32" t="str">
-        <v/>
+        <v>Design</v>
       </c>
       <c r="M32" t="str">
         <v/>
       </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>3</v>
+      <c r="A33" t="str">
+        <v>Item</v>
       </c>
       <c r="B33" t="str">
-        <v>Development</v>
-      </c>
-      <c r="C33">
-        <v>24590</v>
-      </c>
-      <c r="D33">
-        <v>109</v>
-      </c>
-      <c r="E33" t="str">
-        <v/>
+        <v>Two rounds of design feedback</v>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v>Design</v>
+      </c>
+      <c r="E33">
+        <v>4</v>
       </c>
       <c r="F33" t="str">
-        <v/>
+        <v>Project Management</v>
       </c>
       <c r="G33">
-        <v>97</v>
+        <v>2</v>
       </c>
       <c r="H33" t="str">
         <v/>
@@ -1758,36 +1950,42 @@
         <v/>
       </c>
       <c r="K33">
-        <v>12</v>
+        <v>1260</v>
       </c>
       <c r="L33" t="str">
-        <v/>
+        <v>Design</v>
       </c>
       <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B34" t="str">
-        <v>WordPress install and dev, staging environment setup</v>
+        <v>Client sign-off and approval</v>
       </c>
       <c r="C34" t="str">
         <v/>
       </c>
-      <c r="D34">
-        <v>2</v>
-      </c>
-      <c r="E34" t="str">
-        <v/>
+      <c r="D34" t="str">
+        <v>Project Management</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
       </c>
       <c r="F34" t="str">
         <v/>
       </c>
-      <c r="G34">
-        <v>2</v>
+      <c r="G34" t="str">
+        <v/>
       </c>
       <c r="H34" t="str">
         <v/>
@@ -1798,28 +1996,34 @@
       <c r="J34" t="str">
         <v/>
       </c>
-      <c r="K34" t="str">
-        <v/>
+      <c r="K34">
+        <v>210</v>
       </c>
       <c r="L34" t="str">
-        <v/>
-      </c>
-      <c r="M34">
-        <v>460</v>
+        <v>Design</v>
+      </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v/>
+        <v>Spacer</v>
       </c>
       <c r="B35" t="str">
-        <v>Install and configure core plugins</v>
+        <v/>
       </c>
       <c r="C35" t="str">
         <v/>
       </c>
-      <c r="D35">
-        <v>3</v>
+      <c r="D35" t="str">
+        <v/>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1827,8 +2031,8 @@
       <c r="F35" t="str">
         <v/>
       </c>
-      <c r="G35">
-        <v>3</v>
+      <c r="G35" t="str">
+        <v/>
       </c>
       <c r="H35" t="str">
         <v/>
@@ -1845,22 +2049,28 @@
       <c r="L35" t="str">
         <v/>
       </c>
-      <c r="M35">
-        <v>690</v>
+      <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v/>
+        <v>Header</v>
       </c>
       <c r="B36" t="str">
-        <v>Apply custom WordPress theme from approved designs</v>
-      </c>
-      <c r="C36" t="str">
-        <v/>
-      </c>
-      <c r="D36">
-        <v>6</v>
+        <v>Development</v>
+      </c>
+      <c r="C36">
+        <v>28440</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1868,8 +2078,8 @@
       <c r="F36" t="str">
         <v/>
       </c>
-      <c r="G36">
-        <v>6</v>
+      <c r="G36" t="str">
+        <v/>
       </c>
       <c r="H36" t="str">
         <v/>
@@ -1884,33 +2094,39 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v/>
-      </c>
-      <c r="M36">
-        <v>1380</v>
+        <v>Development</v>
+      </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B37" t="str">
-        <v>Navigation and footer setup</v>
+        <v>WordPress install and dev, staging environment setup</v>
       </c>
       <c r="C37" t="str">
         <v/>
       </c>
-      <c r="D37">
-        <v>6</v>
-      </c>
-      <c r="E37" t="str">
-        <v/>
+      <c r="D37" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
       </c>
       <c r="F37" t="str">
         <v/>
       </c>
-      <c r="G37">
-        <v>6</v>
+      <c r="G37" t="str">
+        <v/>
       </c>
       <c r="H37" t="str">
         <v/>
@@ -1921,37 +2137,43 @@
       <c r="J37" t="str">
         <v/>
       </c>
-      <c r="K37" t="str">
-        <v/>
+      <c r="K37">
+        <v>460</v>
       </c>
       <c r="L37" t="str">
-        <v/>
-      </c>
-      <c r="M37">
-        <v>1380</v>
+        <v>Development</v>
+      </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B38" t="str">
-        <v>Favicon and breadcrumbs (schema markup if required per QLD government guidelines)</v>
+        <v>Install and configure core plugins</v>
       </c>
       <c r="C38" t="str">
         <v/>
       </c>
-      <c r="D38">
-        <v>2</v>
-      </c>
-      <c r="E38" t="str">
-        <v/>
+      <c r="D38" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E38">
+        <v>3</v>
       </c>
       <c r="F38" t="str">
         <v/>
       </c>
-      <c r="G38">
-        <v>2</v>
+      <c r="G38" t="str">
+        <v/>
       </c>
       <c r="H38" t="str">
         <v/>
@@ -1962,37 +2184,43 @@
       <c r="J38" t="str">
         <v/>
       </c>
-      <c r="K38" t="str">
-        <v/>
+      <c r="K38">
+        <v>690</v>
       </c>
       <c r="L38" t="str">
-        <v/>
-      </c>
-      <c r="M38">
-        <v>460</v>
+        <v>Development</v>
+      </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B39" t="str">
-        <v>User roles (Admin, Author, Standard)</v>
+        <v>Apply custom WordPress theme from approved designs</v>
       </c>
       <c r="C39" t="str">
         <v/>
       </c>
-      <c r="D39">
-        <v>5</v>
-      </c>
-      <c r="E39" t="str">
-        <v/>
+      <c r="D39" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E39">
+        <v>6</v>
       </c>
       <c r="F39" t="str">
         <v/>
       </c>
-      <c r="G39">
-        <v>5</v>
+      <c r="G39" t="str">
+        <v/>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -2003,37 +2231,43 @@
       <c r="J39" t="str">
         <v/>
       </c>
-      <c r="K39" t="str">
-        <v/>
+      <c r="K39">
+        <v>1380</v>
       </c>
       <c r="L39" t="str">
-        <v/>
-      </c>
-      <c r="M39">
-        <v>1150</v>
+        <v>Development</v>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B40" t="str">
-        <v>Custom post types (structure confirmed post-blueprint)</v>
+        <v>Navigation and footer setup</v>
       </c>
       <c r="C40" t="str">
         <v/>
       </c>
-      <c r="D40">
-        <v>5</v>
-      </c>
-      <c r="E40" t="str">
-        <v/>
+      <c r="D40" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E40">
+        <v>6</v>
       </c>
       <c r="F40" t="str">
         <v/>
       </c>
-      <c r="G40">
-        <v>5</v>
+      <c r="G40" t="str">
+        <v/>
       </c>
       <c r="H40" t="str">
         <v/>
@@ -2044,37 +2278,43 @@
       <c r="J40" t="str">
         <v/>
       </c>
-      <c r="K40" t="str">
-        <v/>
+      <c r="K40">
+        <v>1380</v>
       </c>
       <c r="L40" t="str">
-        <v/>
-      </c>
-      <c r="M40">
-        <v>1150</v>
+        <v>Development</v>
+      </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B41" t="str">
-        <v>Taxonomy structure and setup (e.g. content type, topic and journey level)</v>
+        <v>Favicon and breadcrumbs (schema markup if required per QLD government guidelines)</v>
       </c>
       <c r="C41" t="str">
         <v/>
       </c>
-      <c r="D41">
-        <v>6</v>
-      </c>
-      <c r="E41" t="str">
-        <v/>
+      <c r="D41" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E41">
+        <v>2</v>
       </c>
       <c r="F41" t="str">
         <v/>
       </c>
-      <c r="G41">
-        <v>6</v>
+      <c r="G41" t="str">
+        <v/>
       </c>
       <c r="H41" t="str">
         <v/>
@@ -2085,37 +2325,43 @@
       <c r="J41" t="str">
         <v/>
       </c>
-      <c r="K41" t="str">
-        <v/>
+      <c r="K41">
+        <v>460</v>
       </c>
       <c r="L41" t="str">
-        <v/>
-      </c>
-      <c r="M41">
-        <v>1380</v>
+        <v>Development</v>
+      </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B42" t="str">
-        <v>Post-login homepage, journey selection interface</v>
+        <v>User roles (Admin, Author, Standard)</v>
       </c>
       <c r="C42" t="str">
         <v/>
       </c>
-      <c r="D42">
-        <v>3</v>
-      </c>
-      <c r="E42" t="str">
-        <v/>
+      <c r="D42" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E42">
+        <v>5</v>
       </c>
       <c r="F42" t="str">
         <v/>
       </c>
-      <c r="G42">
-        <v>3</v>
+      <c r="G42" t="str">
+        <v/>
       </c>
       <c r="H42" t="str">
         <v/>
@@ -2126,37 +2372,43 @@
       <c r="J42" t="str">
         <v/>
       </c>
-      <c r="K42" t="str">
-        <v/>
+      <c r="K42">
+        <v>1150</v>
       </c>
       <c r="L42" t="str">
-        <v/>
-      </c>
-      <c r="M42">
-        <v>690</v>
+        <v>Development</v>
+      </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B43" t="str">
-        <v>Journey home pages, tailored content per path</v>
+        <v>Custom post types (structure confirmed post-blueprint)</v>
       </c>
       <c r="C43" t="str">
         <v/>
       </c>
-      <c r="D43">
-        <v>4</v>
-      </c>
-      <c r="E43" t="str">
-        <v/>
+      <c r="D43" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E43">
+        <v>5</v>
       </c>
       <c r="F43" t="str">
         <v/>
       </c>
-      <c r="G43">
-        <v>4</v>
+      <c r="G43" t="str">
+        <v/>
       </c>
       <c r="H43" t="str">
         <v/>
@@ -2167,37 +2419,43 @@
       <c r="J43" t="str">
         <v/>
       </c>
-      <c r="K43" t="str">
-        <v/>
+      <c r="K43">
+        <v>1150</v>
       </c>
       <c r="L43" t="str">
-        <v/>
-      </c>
-      <c r="M43">
-        <v>920</v>
+        <v>Development</v>
+      </c>
+      <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B44" t="str">
-        <v>Resource library, filterable browse and search by content type, topic and level</v>
+        <v>Taxonomy structure and setup (e.g. content type, topic and journey level)</v>
       </c>
       <c r="C44" t="str">
         <v/>
       </c>
-      <c r="D44">
-        <v>8</v>
-      </c>
-      <c r="E44" t="str">
-        <v/>
+      <c r="D44" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E44">
+        <v>6</v>
       </c>
       <c r="F44" t="str">
         <v/>
       </c>
-      <c r="G44">
-        <v>8</v>
+      <c r="G44" t="str">
+        <v/>
       </c>
       <c r="H44" t="str">
         <v/>
@@ -2208,37 +2466,43 @@
       <c r="J44" t="str">
         <v/>
       </c>
-      <c r="K44" t="str">
-        <v/>
+      <c r="K44">
+        <v>1380</v>
       </c>
       <c r="L44" t="str">
-        <v/>
-      </c>
-      <c r="M44">
-        <v>1840</v>
+        <v>Development</v>
+      </c>
+      <c r="M44" t="str">
+        <v/>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B45" t="str">
-        <v>Resource detail view</v>
+        <v>Post-login homepage, journey selection interface</v>
       </c>
       <c r="C45" t="str">
         <v/>
       </c>
-      <c r="D45">
+      <c r="D45" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E45">
         <v>3</v>
       </c>
-      <c r="E45" t="str">
-        <v/>
-      </c>
       <c r="F45" t="str">
         <v/>
       </c>
-      <c r="G45">
-        <v>3</v>
+      <c r="G45" t="str">
+        <v/>
       </c>
       <c r="H45" t="str">
         <v/>
@@ -2249,37 +2513,43 @@
       <c r="J45" t="str">
         <v/>
       </c>
-      <c r="K45" t="str">
-        <v/>
+      <c r="K45">
+        <v>690</v>
       </c>
       <c r="L45" t="str">
-        <v/>
-      </c>
-      <c r="M45">
-        <v>690</v>
+        <v>Development</v>
+      </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B46" t="str">
-        <v>Section pages, auto-populate content by taxonomy</v>
+        <v>Taxonomy landing pages, content aggregated by topic and category</v>
       </c>
       <c r="C46" t="str">
         <v/>
       </c>
-      <c r="D46">
-        <v>3</v>
-      </c>
-      <c r="E46" t="str">
-        <v/>
+      <c r="D46" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E46">
+        <v>4</v>
       </c>
       <c r="F46" t="str">
         <v/>
       </c>
-      <c r="G46">
-        <v>3</v>
+      <c r="G46" t="str">
+        <v/>
       </c>
       <c r="H46" t="str">
         <v/>
@@ -2290,37 +2560,43 @@
       <c r="J46" t="str">
         <v/>
       </c>
-      <c r="K46" t="str">
-        <v/>
+      <c r="K46">
+        <v>920</v>
       </c>
       <c r="L46" t="str">
-        <v/>
-      </c>
-      <c r="M46">
-        <v>690</v>
+        <v>Development</v>
+      </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B47" t="str">
-        <v>Site search, filtered and taxonomy-aware</v>
+        <v>Resource library, filterable browse and search by content type, topic and level</v>
       </c>
       <c r="C47" t="str">
         <v/>
       </c>
-      <c r="D47">
-        <v>4</v>
-      </c>
-      <c r="E47" t="str">
-        <v/>
+      <c r="D47" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E47">
+        <v>8</v>
       </c>
       <c r="F47" t="str">
         <v/>
       </c>
-      <c r="G47">
-        <v>4</v>
+      <c r="G47" t="str">
+        <v/>
       </c>
       <c r="H47" t="str">
         <v/>
@@ -2331,37 +2607,43 @@
       <c r="J47" t="str">
         <v/>
       </c>
-      <c r="K47" t="str">
-        <v/>
+      <c r="K47">
+        <v>1840</v>
       </c>
       <c r="L47" t="str">
-        <v/>
-      </c>
-      <c r="M47">
-        <v>920</v>
+        <v>Development</v>
+      </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B48" t="str">
-        <v>Last updated timestamps on all content</v>
+        <v>Resource detail view</v>
       </c>
       <c r="C48" t="str">
         <v/>
       </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-      <c r="E48" t="str">
-        <v/>
+      <c r="D48" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E48">
+        <v>3</v>
       </c>
       <c r="F48" t="str">
         <v/>
       </c>
-      <c r="G48">
-        <v>1</v>
+      <c r="G48" t="str">
+        <v/>
       </c>
       <c r="H48" t="str">
         <v/>
@@ -2372,37 +2654,43 @@
       <c r="J48" t="str">
         <v/>
       </c>
-      <c r="K48" t="str">
-        <v/>
+      <c r="K48">
+        <v>690</v>
       </c>
       <c r="L48" t="str">
-        <v/>
-      </c>
-      <c r="M48">
-        <v>230</v>
+        <v>Development</v>
+      </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B49" t="str">
-        <v>Content revision history, versioning for all content types</v>
+        <v>Section pages, auto-populate content by taxonomy</v>
       </c>
       <c r="C49" t="str">
         <v/>
       </c>
-      <c r="D49">
-        <v>4</v>
-      </c>
-      <c r="E49" t="str">
-        <v/>
+      <c r="D49" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E49">
+        <v>3</v>
       </c>
       <c r="F49" t="str">
         <v/>
       </c>
-      <c r="G49">
-        <v>4</v>
+      <c r="G49" t="str">
+        <v/>
       </c>
       <c r="H49" t="str">
         <v/>
@@ -2413,37 +2701,43 @@
       <c r="J49" t="str">
         <v/>
       </c>
-      <c r="K49" t="str">
-        <v/>
+      <c r="K49">
+        <v>690</v>
       </c>
       <c r="L49" t="str">
-        <v/>
-      </c>
-      <c r="M49">
-        <v>920</v>
+        <v>Development</v>
+      </c>
+      <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B50" t="str">
-        <v>Access logging and automated log pruning configuration</v>
+        <v>Site search, filtered and taxonomy-aware</v>
       </c>
       <c r="C50" t="str">
         <v/>
       </c>
-      <c r="D50">
+      <c r="D50" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E50">
         <v>4</v>
       </c>
-      <c r="E50" t="str">
-        <v/>
-      </c>
       <c r="F50" t="str">
         <v/>
       </c>
-      <c r="G50">
-        <v>4</v>
+      <c r="G50" t="str">
+        <v/>
       </c>
       <c r="H50" t="str">
         <v/>
@@ -2454,37 +2748,43 @@
       <c r="J50" t="str">
         <v/>
       </c>
-      <c r="K50" t="str">
-        <v/>
+      <c r="K50">
+        <v>920</v>
       </c>
       <c r="L50" t="str">
-        <v/>
-      </c>
-      <c r="M50">
-        <v>920</v>
+        <v>Development</v>
+      </c>
+      <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B51" t="str">
-        <v>Content feedback, relevance rating on resources</v>
+        <v>Last updated timestamps on all content</v>
       </c>
       <c r="C51" t="str">
         <v/>
       </c>
-      <c r="D51">
-        <v>2</v>
-      </c>
-      <c r="E51" t="str">
-        <v/>
+      <c r="D51" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
       </c>
       <c r="F51" t="str">
         <v/>
       </c>
-      <c r="G51">
-        <v>2</v>
+      <c r="G51" t="str">
+        <v/>
       </c>
       <c r="H51" t="str">
         <v/>
@@ -2495,37 +2795,43 @@
       <c r="J51" t="str">
         <v/>
       </c>
-      <c r="K51" t="str">
-        <v/>
+      <c r="K51">
+        <v>230</v>
       </c>
       <c r="L51" t="str">
-        <v/>
-      </c>
-      <c r="M51">
-        <v>460</v>
+        <v>Development</v>
+      </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B52" t="str">
-        <v>User feedback form (Gravity Forms)</v>
+        <v>Content revision history, versioning for all content types</v>
       </c>
       <c r="C52" t="str">
         <v/>
       </c>
-      <c r="D52">
-        <v>3</v>
-      </c>
-      <c r="E52" t="str">
-        <v/>
+      <c r="D52" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E52">
+        <v>4</v>
       </c>
       <c r="F52" t="str">
         <v/>
       </c>
-      <c r="G52">
-        <v>3</v>
+      <c r="G52" t="str">
+        <v/>
       </c>
       <c r="H52" t="str">
         <v/>
@@ -2536,37 +2842,43 @@
       <c r="J52" t="str">
         <v/>
       </c>
-      <c r="K52" t="str">
-        <v/>
+      <c r="K52">
+        <v>920</v>
       </c>
       <c r="L52" t="str">
-        <v/>
-      </c>
-      <c r="M52">
-        <v>690</v>
+        <v>Development</v>
+      </c>
+      <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B53" t="str">
-        <v>Responsive build and testing across all breakpoints</v>
+        <v>Access logging and automated log pruning configuration</v>
       </c>
       <c r="C53" t="str">
         <v/>
       </c>
-      <c r="D53">
+      <c r="D53" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E53">
         <v>4</v>
       </c>
-      <c r="E53" t="str">
-        <v/>
-      </c>
       <c r="F53" t="str">
         <v/>
       </c>
-      <c r="G53">
-        <v>4</v>
+      <c r="G53" t="str">
+        <v/>
       </c>
       <c r="H53" t="str">
         <v/>
@@ -2577,37 +2889,43 @@
       <c r="J53" t="str">
         <v/>
       </c>
-      <c r="K53" t="str">
-        <v/>
+      <c r="K53">
+        <v>920</v>
       </c>
       <c r="L53" t="str">
-        <v/>
-      </c>
-      <c r="M53">
-        <v>920</v>
+        <v>Development</v>
+      </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B54" t="str">
-        <v>Print CSS</v>
+        <v>Content feedback, relevance rating on resources</v>
       </c>
       <c r="C54" t="str">
         <v/>
       </c>
-      <c r="D54">
-        <v>8</v>
-      </c>
-      <c r="E54" t="str">
-        <v/>
+      <c r="D54" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E54">
+        <v>2</v>
       </c>
       <c r="F54" t="str">
         <v/>
       </c>
-      <c r="G54">
-        <v>8</v>
+      <c r="G54" t="str">
+        <v/>
       </c>
       <c r="H54" t="str">
         <v/>
@@ -2618,37 +2936,43 @@
       <c r="J54" t="str">
         <v/>
       </c>
-      <c r="K54" t="str">
-        <v/>
+      <c r="K54">
+        <v>460</v>
       </c>
       <c r="L54" t="str">
-        <v/>
-      </c>
-      <c r="M54">
-        <v>1840</v>
+        <v>Development</v>
+      </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B55" t="str">
-        <v>WCAG AA implementation throughout</v>
+        <v>User feedback form (Gravity Forms)</v>
       </c>
       <c r="C55" t="str">
         <v/>
       </c>
-      <c r="D55">
-        <v>5</v>
-      </c>
-      <c r="E55" t="str">
-        <v/>
+      <c r="D55" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E55">
+        <v>3</v>
       </c>
       <c r="F55" t="str">
         <v/>
       </c>
-      <c r="G55">
-        <v>5</v>
+      <c r="G55" t="str">
+        <v/>
       </c>
       <c r="H55" t="str">
         <v/>
@@ -2659,37 +2983,43 @@
       <c r="J55" t="str">
         <v/>
       </c>
-      <c r="K55" t="str">
-        <v/>
+      <c r="K55">
+        <v>690</v>
       </c>
       <c r="L55" t="str">
-        <v/>
-      </c>
-      <c r="M55">
-        <v>1150</v>
+        <v>Development</v>
+      </c>
+      <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B56" t="str">
-        <v>Standard pages x 2</v>
+        <v>Responsive build and testing across all breakpoints</v>
       </c>
       <c r="C56" t="str">
         <v/>
       </c>
-      <c r="D56">
-        <v>6</v>
-      </c>
-      <c r="E56" t="str">
-        <v/>
+      <c r="D56" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E56">
+        <v>4</v>
       </c>
       <c r="F56" t="str">
         <v/>
       </c>
-      <c r="G56">
-        <v>6</v>
+      <c r="G56" t="str">
+        <v/>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -2700,31 +3030,37 @@
       <c r="J56" t="str">
         <v/>
       </c>
-      <c r="K56" t="str">
-        <v/>
+      <c r="K56">
+        <v>920</v>
       </c>
       <c r="L56" t="str">
-        <v/>
-      </c>
-      <c r="M56">
-        <v>1380</v>
+        <v>Development</v>
+      </c>
+      <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B57" t="str">
-        <v>Project management throughout build</v>
+        <v>Print CSS</v>
       </c>
       <c r="C57" t="str">
         <v/>
       </c>
-      <c r="D57">
-        <v>12</v>
-      </c>
-      <c r="E57" t="str">
-        <v/>
+      <c r="D57" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E57">
+        <v>8</v>
       </c>
       <c r="F57" t="str">
         <v/>
@@ -2742,30 +3078,36 @@
         <v/>
       </c>
       <c r="K57">
-        <v>12</v>
+        <v>1840</v>
       </c>
       <c r="L57" t="str">
-        <v/>
-      </c>
-      <c r="M57">
-        <v>2280</v>
+        <v>Development</v>
+      </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>WCAG AA implementation throughout</v>
       </c>
       <c r="C58" t="str">
         <v/>
       </c>
       <c r="D58" t="str">
-        <v/>
-      </c>
-      <c r="E58" t="str">
-        <v/>
+        <v>Development</v>
+      </c>
+      <c r="E58">
+        <v>5</v>
       </c>
       <c r="F58" t="str">
         <v/>
@@ -2782,31 +3124,37 @@
       <c r="J58" t="str">
         <v/>
       </c>
-      <c r="K58" t="str">
-        <v/>
+      <c r="K58">
+        <v>1150</v>
       </c>
       <c r="L58" t="str">
-        <v/>
+        <v>Development</v>
       </c>
       <c r="M58" t="str">
         <v/>
       </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
-      <c r="A59">
-        <v>4</v>
+      <c r="A59" t="str">
+        <v>Item</v>
       </c>
       <c r="B59" t="str">
-        <v>Content and Training</v>
-      </c>
-      <c r="C59">
-        <v>2030</v>
-      </c>
-      <c r="D59">
-        <v>11</v>
-      </c>
-      <c r="E59" t="str">
-        <v/>
+        <v>Standard pages x 2</v>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E59">
+        <v>6</v>
       </c>
       <c r="F59" t="str">
         <v/>
@@ -2817,37 +3165,43 @@
       <c r="H59" t="str">
         <v/>
       </c>
-      <c r="I59">
-        <v>6</v>
+      <c r="I59" t="str">
+        <v/>
       </c>
       <c r="J59" t="str">
         <v/>
       </c>
       <c r="K59">
-        <v>5</v>
+        <v>1380</v>
       </c>
       <c r="L59" t="str">
-        <v/>
+        <v>Development</v>
       </c>
       <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B60" t="str">
-        <v>Sample content entry during handover (up to 6hrs)</v>
+        <v>SSO via Active Directory integration (subject to DTET IT cooperation)</v>
       </c>
       <c r="C60" t="str">
         <v/>
       </c>
-      <c r="D60">
-        <v>6</v>
-      </c>
-      <c r="E60" t="str">
-        <v/>
+      <c r="D60" t="str">
+        <v>Integration &amp; Technical</v>
+      </c>
+      <c r="E60">
+        <v>8</v>
       </c>
       <c r="F60" t="str">
         <v/>
@@ -2858,38 +3212,44 @@
       <c r="H60" t="str">
         <v/>
       </c>
-      <c r="I60">
-        <v>6</v>
+      <c r="I60" t="str">
+        <v/>
       </c>
       <c r="J60" t="str">
         <v/>
       </c>
-      <c r="K60" t="str">
-        <v/>
+      <c r="K60">
+        <v>2000</v>
       </c>
       <c r="L60" t="str">
-        <v/>
-      </c>
-      <c r="M60">
-        <v>1080</v>
+        <v>Development</v>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B61" t="str">
-        <v>Training materials and site-specific documentation</v>
+        <v>Content search and bulk replace tool</v>
       </c>
       <c r="C61" t="str">
         <v/>
       </c>
-      <c r="D61">
+      <c r="D61" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E61">
         <v>2</v>
       </c>
-      <c r="E61" t="str">
-        <v/>
-      </c>
       <c r="F61" t="str">
         <v/>
       </c>
@@ -2906,30 +3266,36 @@
         <v/>
       </c>
       <c r="K61">
-        <v>2</v>
+        <v>460</v>
       </c>
       <c r="L61" t="str">
-        <v/>
-      </c>
-      <c r="M61">
-        <v>380</v>
+        <v>Development</v>
+      </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B62" t="str">
-        <v>Training session 1 via Zoom (1.5hrs)</v>
+        <v>Link sharing on resources (shareable URLs, copy link)</v>
       </c>
       <c r="C62" t="str">
         <v/>
       </c>
-      <c r="D62">
-        <v>1.5</v>
-      </c>
-      <c r="E62" t="str">
-        <v/>
+      <c r="D62" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
       </c>
       <c r="F62" t="str">
         <v/>
@@ -2947,30 +3313,36 @@
         <v/>
       </c>
       <c r="K62">
-        <v>1.5</v>
+        <v>460</v>
       </c>
       <c r="L62" t="str">
-        <v/>
-      </c>
-      <c r="M62">
-        <v>285</v>
+        <v>Development</v>
+      </c>
+      <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B63" t="str">
-        <v>Training session 2 via Zoom if required (1.5hrs)</v>
+        <v>Quick links navigation panel</v>
       </c>
       <c r="C63" t="str">
         <v/>
       </c>
-      <c r="D63">
-        <v>1.5</v>
-      </c>
-      <c r="E63" t="str">
-        <v/>
+      <c r="D63" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E63">
+        <v>3</v>
       </c>
       <c r="F63" t="str">
         <v/>
@@ -2988,30 +3360,36 @@
         <v/>
       </c>
       <c r="K63">
-        <v>1.5</v>
+        <v>690</v>
       </c>
       <c r="L63" t="str">
-        <v/>
-      </c>
-      <c r="M63">
-        <v>285</v>
+        <v>Development</v>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>Project management throughout build</v>
       </c>
       <c r="C64" t="str">
         <v/>
       </c>
       <c r="D64" t="str">
-        <v/>
-      </c>
-      <c r="E64" t="str">
-        <v/>
+        <v>Project Management</v>
+      </c>
+      <c r="E64">
+        <v>12</v>
       </c>
       <c r="F64" t="str">
         <v/>
@@ -3028,28 +3406,34 @@
       <c r="J64" t="str">
         <v/>
       </c>
-      <c r="K64" t="str">
-        <v/>
+      <c r="K64">
+        <v>2520</v>
       </c>
       <c r="L64" t="str">
-        <v/>
+        <v>Development</v>
       </c>
       <c r="M64" t="str">
         <v/>
       </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
-      <c r="A65">
-        <v>5</v>
+      <c r="A65" t="str">
+        <v>Spacer</v>
       </c>
       <c r="B65" t="str">
-        <v>Golive and Delivery</v>
-      </c>
-      <c r="C65">
-        <v>4670</v>
-      </c>
-      <c r="D65">
-        <v>21</v>
+        <v/>
+      </c>
+      <c r="C65" t="str">
+        <v/>
+      </c>
+      <c r="D65" t="str">
+        <v/>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -3057,11 +3441,11 @@
       <c r="F65" t="str">
         <v/>
       </c>
-      <c r="G65">
-        <v>2</v>
-      </c>
-      <c r="H65">
-        <v>15</v>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v/>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -3069,28 +3453,34 @@
       <c r="J65" t="str">
         <v/>
       </c>
-      <c r="K65">
-        <v>4</v>
+      <c r="K65" t="str">
+        <v/>
       </c>
       <c r="L65" t="str">
         <v/>
       </c>
       <c r="M65" t="str">
+        <v/>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v/>
+        <v>Header</v>
       </c>
       <c r="B66" t="str">
-        <v>QA across target browsers and devices</v>
-      </c>
-      <c r="C66" t="str">
-        <v/>
-      </c>
-      <c r="D66">
-        <v>8</v>
+        <v>Content and Training</v>
+      </c>
+      <c r="C66">
+        <v>2070</v>
+      </c>
+      <c r="D66" t="str">
+        <v/>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -3101,8 +3491,8 @@
       <c r="G66" t="str">
         <v/>
       </c>
-      <c r="H66">
-        <v>8</v>
+      <c r="H66" t="str">
+        <v/>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -3114,27 +3504,33 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v/>
-      </c>
-      <c r="M66">
-        <v>1840</v>
+        <v>Content and Training</v>
+      </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B67" t="str">
-        <v>WCAG AA accessibility checks (12 key pages)</v>
+        <v>Sample content entry during handover (up to 6hrs)</v>
       </c>
       <c r="C67" t="str">
         <v/>
       </c>
-      <c r="D67">
-        <v>4</v>
-      </c>
-      <c r="E67" t="str">
-        <v/>
+      <c r="D67" t="str">
+        <v>Content Entry</v>
+      </c>
+      <c r="E67">
+        <v>6</v>
       </c>
       <c r="F67" t="str">
         <v/>
@@ -3142,8 +3538,8 @@
       <c r="G67" t="str">
         <v/>
       </c>
-      <c r="H67">
-        <v>4</v>
+      <c r="H67" t="str">
+        <v/>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -3151,31 +3547,37 @@
       <c r="J67" t="str">
         <v/>
       </c>
-      <c r="K67" t="str">
-        <v/>
+      <c r="K67">
+        <v>1020</v>
       </c>
       <c r="L67" t="str">
-        <v/>
-      </c>
-      <c r="M67">
-        <v>920</v>
+        <v>Content and Training</v>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B68" t="str">
-        <v>Post-golive QA</v>
+        <v>Training materials and site-specific documentation</v>
       </c>
       <c r="C68" t="str">
         <v/>
       </c>
-      <c r="D68">
-        <v>3</v>
-      </c>
-      <c r="E68" t="str">
-        <v/>
+      <c r="D68" t="str">
+        <v>Project Management</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
       </c>
       <c r="F68" t="str">
         <v/>
@@ -3183,8 +3585,8 @@
       <c r="G68" t="str">
         <v/>
       </c>
-      <c r="H68">
-        <v>3</v>
+      <c r="H68" t="str">
+        <v/>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -3192,31 +3594,37 @@
       <c r="J68" t="str">
         <v/>
       </c>
-      <c r="K68" t="str">
-        <v/>
+      <c r="K68">
+        <v>420</v>
       </c>
       <c r="L68" t="str">
-        <v/>
-      </c>
-      <c r="M68">
-        <v>690</v>
+        <v>Content and Training</v>
+      </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B69" t="str">
-        <v>Client access for user acceptance testing (UAT)</v>
+        <v>Training session 1 via Zoom (1.5hrs)</v>
       </c>
       <c r="C69" t="str">
         <v/>
       </c>
-      <c r="D69">
-        <v>1</v>
-      </c>
-      <c r="E69" t="str">
-        <v/>
+      <c r="D69" t="str">
+        <v>Project Management</v>
+      </c>
+      <c r="E69">
+        <v>1.5</v>
       </c>
       <c r="F69" t="str">
         <v/>
@@ -3234,36 +3642,42 @@
         <v/>
       </c>
       <c r="K69">
-        <v>1</v>
+        <v>315</v>
       </c>
       <c r="L69" t="str">
-        <v/>
-      </c>
-      <c r="M69">
-        <v>190</v>
+        <v>Content and Training</v>
+      </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B70" t="str">
-        <v>Golive procedures and final security checks</v>
+        <v>Training session 2 via Zoom if required (1.5hrs)</v>
       </c>
       <c r="C70" t="str">
         <v/>
       </c>
-      <c r="D70">
-        <v>2</v>
-      </c>
-      <c r="E70" t="str">
-        <v/>
+      <c r="D70" t="str">
+        <v>Project Management</v>
+      </c>
+      <c r="E70">
+        <v>1.5</v>
       </c>
       <c r="F70" t="str">
         <v/>
       </c>
-      <c r="G70">
-        <v>2</v>
+      <c r="G70" t="str">
+        <v/>
       </c>
       <c r="H70" t="str">
         <v/>
@@ -3274,28 +3688,34 @@
       <c r="J70" t="str">
         <v/>
       </c>
-      <c r="K70" t="str">
-        <v/>
+      <c r="K70">
+        <v>315</v>
       </c>
       <c r="L70" t="str">
-        <v/>
-      </c>
-      <c r="M70">
-        <v>460</v>
+        <v>Content and Training</v>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v/>
+        <v>Spacer</v>
       </c>
       <c r="B71" t="str">
-        <v>Handover and delivery documentation</v>
+        <v/>
       </c>
       <c r="C71" t="str">
         <v/>
       </c>
-      <c r="D71">
-        <v>3</v>
+      <c r="D71" t="str">
+        <v/>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3315,25 +3735,31 @@
       <c r="J71" t="str">
         <v/>
       </c>
-      <c r="K71">
-        <v>3</v>
+      <c r="K71" t="str">
+        <v/>
       </c>
       <c r="L71" t="str">
         <v/>
       </c>
-      <c r="M71">
-        <v>570</v>
+      <c r="M71" t="str">
+        <v/>
+      </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v/>
+        <v>Header</v>
       </c>
       <c r="B72" t="str">
-        <v/>
-      </c>
-      <c r="C72" t="str">
-        <v/>
+        <v>Golive and Delivery</v>
+      </c>
+      <c r="C72">
+        <v>3850</v>
       </c>
       <c r="D72" t="str">
         <v/>
@@ -3360,27 +3786,33 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v/>
+        <v>Golive and Delivery</v>
       </c>
       <c r="M72" t="str">
+        <v/>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>-</v>
+        <v>Item</v>
       </c>
       <c r="B73" t="str">
-        <v>SUBTOTAL (ex GST)</v>
-      </c>
-      <c r="C73">
-        <v>48790</v>
+        <v>QA across target browsers and devices</v>
+      </c>
+      <c r="C73" t="str">
+        <v/>
       </c>
       <c r="D73" t="str">
-        <v/>
-      </c>
-      <c r="E73" t="str">
-        <v/>
+        <v>Quality Assurance</v>
+      </c>
+      <c r="E73">
+        <v>8</v>
       </c>
       <c r="F73" t="str">
         <v/>
@@ -3397,31 +3829,37 @@
       <c r="J73" t="str">
         <v/>
       </c>
-      <c r="K73" t="str">
-        <v/>
+      <c r="K73">
+        <v>1360</v>
       </c>
       <c r="L73" t="str">
-        <v/>
-      </c>
-      <c r="M73">
-        <v>48790</v>
+        <v>Golive and Delivery</v>
+      </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B74" t="str">
-        <v/>
+        <v>WCAG AA accessibility checks (12 key pages)</v>
       </c>
       <c r="C74" t="str">
         <v/>
       </c>
       <c r="D74" t="str">
-        <v/>
-      </c>
-      <c r="E74" t="str">
-        <v/>
+        <v>Quality Assurance</v>
+      </c>
+      <c r="E74">
+        <v>4</v>
       </c>
       <c r="F74" t="str">
         <v/>
@@ -3438,31 +3876,37 @@
       <c r="J74" t="str">
         <v/>
       </c>
-      <c r="K74" t="str">
-        <v/>
+      <c r="K74">
+        <v>680</v>
       </c>
       <c r="L74" t="str">
-        <v/>
+        <v>Golive and Delivery</v>
       </c>
       <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B75" t="str">
-        <v>Optional / Phase 2 (indicative, not included above)</v>
+        <v>Post-golive QA</v>
       </c>
       <c r="C75" t="str">
         <v/>
       </c>
       <c r="D75" t="str">
-        <v/>
-      </c>
-      <c r="E75" t="str">
-        <v/>
+        <v>Quality Assurance</v>
+      </c>
+      <c r="E75">
+        <v>3</v>
       </c>
       <c r="F75" t="str">
         <v/>
@@ -3479,31 +3923,37 @@
       <c r="J75" t="str">
         <v/>
       </c>
-      <c r="K75" t="str">
-        <v/>
+      <c r="K75">
+        <v>510</v>
       </c>
       <c r="L75" t="str">
-        <v/>
+        <v>Golive and Delivery</v>
       </c>
       <c r="M75" t="str">
+        <v/>
+      </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B76" t="str">
-        <v>SSO via Orion/QSS/AD integration (subject to QSS cooperation)</v>
+        <v>Client access for user acceptance testing (UAT)</v>
       </c>
       <c r="C76" t="str">
-        <v>TBC</v>
+        <v/>
       </c>
       <c r="D76" t="str">
-        <v/>
-      </c>
-      <c r="E76" t="str">
-        <v/>
+        <v>Project Management</v>
+      </c>
+      <c r="E76">
+        <v>1</v>
       </c>
       <c r="F76" t="str">
         <v/>
@@ -3520,31 +3970,37 @@
       <c r="J76" t="str">
         <v/>
       </c>
-      <c r="K76" t="str">
-        <v/>
+      <c r="K76">
+        <v>210</v>
       </c>
       <c r="L76" t="str">
-        <v/>
+        <v>Golive and Delivery</v>
       </c>
       <c r="M76" t="str">
+        <v/>
+      </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B77" t="str">
-        <v>AI conversation capability, to be scoped separately</v>
+        <v>Golive procedures and final security checks</v>
       </c>
       <c r="C77" t="str">
-        <v>TBC</v>
+        <v/>
       </c>
       <c r="D77" t="str">
-        <v/>
-      </c>
-      <c r="E77" t="str">
-        <v/>
+        <v>Development</v>
+      </c>
+      <c r="E77">
+        <v>2</v>
       </c>
       <c r="F77" t="str">
         <v/>
@@ -3561,31 +4017,37 @@
       <c r="J77" t="str">
         <v/>
       </c>
-      <c r="K77" t="str">
-        <v/>
+      <c r="K77">
+        <v>460</v>
       </c>
       <c r="L77" t="str">
-        <v/>
+        <v>Golive and Delivery</v>
       </c>
       <c r="M77" t="str">
+        <v/>
+      </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v/>
+        <v>Item</v>
       </c>
       <c r="B78" t="str">
-        <v/>
+        <v>Handover and delivery documentation</v>
       </c>
       <c r="C78" t="str">
         <v/>
       </c>
       <c r="D78" t="str">
-        <v/>
-      </c>
-      <c r="E78" t="str">
-        <v/>
+        <v>Project Management</v>
+      </c>
+      <c r="E78">
+        <v>3</v>
       </c>
       <c r="F78" t="str">
         <v/>
@@ -3602,25 +4064,31 @@
       <c r="J78" t="str">
         <v/>
       </c>
-      <c r="K78" t="str">
-        <v/>
+      <c r="K78">
+        <v>630</v>
       </c>
       <c r="L78" t="str">
-        <v/>
+        <v>Golive and Delivery</v>
       </c>
       <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>-</v>
+        <v>Spacer</v>
       </c>
       <c r="B79" t="str">
-        <v>SUBTOTAL</v>
-      </c>
-      <c r="C79">
-        <v>48790</v>
+        <v/>
+      </c>
+      <c r="C79" t="str">
+        <v/>
       </c>
       <c r="D79" t="str">
         <v/>
@@ -3650,6 +4118,12 @@
         <v/>
       </c>
       <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
         <v/>
       </c>
     </row>
@@ -3658,10 +4132,10 @@
         <v/>
       </c>
       <c r="B80" t="str">
-        <v>GST</v>
-      </c>
-      <c r="C80">
-        <v>4879</v>
+        <v/>
+      </c>
+      <c r="C80" t="str">
+        <v/>
       </c>
       <c r="D80" t="str">
         <v/>
@@ -3691,6 +4165,12 @@
         <v/>
       </c>
       <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
         <v/>
       </c>
     </row>
@@ -3699,10 +4179,10 @@
         <v/>
       </c>
       <c r="B81" t="str">
-        <v>TOTAL</v>
+        <v>SUBTOTAL (ex GST)</v>
       </c>
       <c r="C81">
-        <v>53669</v>
+        <v>54040</v>
       </c>
       <c r="D81" t="str">
         <v/>
@@ -3732,6 +4212,12 @@
         <v/>
       </c>
       <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
         <v/>
       </c>
     </row>
@@ -3775,19 +4261,25 @@
       <c r="M82" t="str">
         <v/>
       </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
         <v/>
       </c>
       <c r="B83" t="str">
-        <v>Invoice total including markup/profit</v>
-      </c>
-      <c r="C83">
-        <v>53669</v>
+        <v>Optional / Phase 2 (indicative, not included above)</v>
+      </c>
+      <c r="C83" t="str">
+        <v/>
       </c>
       <c r="D83" t="str">
-        <v>inc gst</v>
+        <v/>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3814,6 +4306,12 @@
         <v/>
       </c>
       <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
         <v/>
       </c>
     </row>
@@ -3822,13 +4320,13 @@
         <v/>
       </c>
       <c r="B84" t="str">
-        <v>Estimated hours</v>
-      </c>
-      <c r="C84">
-        <v>227</v>
+        <v>AI conversation capability, to be scoped separately</v>
+      </c>
+      <c r="C84" t="str">
+        <v>TBC</v>
       </c>
       <c r="D84" t="str">
-        <v>hrs</v>
+        <v/>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3855,12 +4353,696 @@
         <v/>
       </c>
       <c r="M84" t="str">
+        <v/>
+      </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v/>
+      </c>
+      <c r="B85" t="str">
+        <v>SharePoint integration or full intranet migration (subject to future scoping)</v>
+      </c>
+      <c r="C85" t="str">
+        <v>TBC</v>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
+      <c r="K85" t="str">
+        <v/>
+      </c>
+      <c r="L85" t="str">
+        <v/>
+      </c>
+      <c r="M85" t="str">
+        <v/>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v/>
+      </c>
+      <c r="B86" t="str">
+        <v/>
+      </c>
+      <c r="C86" t="str">
+        <v/>
+      </c>
+      <c r="D86" t="str">
+        <v/>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+      <c r="J86" t="str">
+        <v/>
+      </c>
+      <c r="K86" t="str">
+        <v/>
+      </c>
+      <c r="L86" t="str">
+        <v/>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v/>
+      </c>
+      <c r="B87" t="str">
+        <v>Optional Add-ons (indicative, not included above)</v>
+      </c>
+      <c r="C87" t="str">
+        <v/>
+      </c>
+      <c r="D87" t="str">
+        <v/>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+      <c r="J87" t="str">
+        <v/>
+      </c>
+      <c r="K87" t="str">
+        <v/>
+      </c>
+      <c r="L87" t="str">
+        <v/>
+      </c>
+      <c r="M87" t="str">
+        <v/>
+      </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v/>
+      </c>
+      <c r="B88" t="str">
+        <v>Per-page content entry</v>
+      </c>
+      <c r="C88" t="str">
+        <v>$85 to $170 per page</v>
+      </c>
+      <c r="D88" t="str">
+        <v/>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+      <c r="J88" t="str">
+        <v/>
+      </c>
+      <c r="K88" t="str">
+        <v/>
+      </c>
+      <c r="L88" t="str">
+        <v/>
+      </c>
+      <c r="M88" t="str">
+        <v/>
+      </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v/>
+      </c>
+      <c r="B89" t="str">
+        <v>Bulk resource import via spreadsheet, CSV upload with taxonomy mapping</v>
+      </c>
+      <c r="C89">
+        <v>1380</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Development</v>
+      </c>
+      <c r="E89">
+        <v>6</v>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
+      <c r="K89" t="str">
+        <v/>
+      </c>
+      <c r="L89" t="str">
+        <v/>
+      </c>
+      <c r="M89" t="str">
+        <v/>
+      </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v/>
+      </c>
+      <c r="B90" t="str">
+        <v/>
+      </c>
+      <c r="C90" t="str">
+        <v/>
+      </c>
+      <c r="D90" t="str">
+        <v/>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90" t="str">
+        <v/>
+      </c>
+      <c r="K90" t="str">
+        <v/>
+      </c>
+      <c r="L90" t="str">
+        <v/>
+      </c>
+      <c r="M90" t="str">
+        <v/>
+      </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v/>
+      </c>
+      <c r="B91" t="str">
+        <v>SUBTOTAL</v>
+      </c>
+      <c r="C91">
+        <v>54040</v>
+      </c>
+      <c r="D91" t="str">
+        <v/>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+      <c r="J91" t="str">
+        <v/>
+      </c>
+      <c r="K91" t="str">
+        <v/>
+      </c>
+      <c r="L91" t="str">
+        <v/>
+      </c>
+      <c r="M91" t="str">
+        <v/>
+      </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v/>
+      </c>
+      <c r="B92" t="str">
+        <v>GST</v>
+      </c>
+      <c r="C92">
+        <v>5404</v>
+      </c>
+      <c r="D92" t="str">
+        <v/>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+      <c r="J92" t="str">
+        <v/>
+      </c>
+      <c r="K92" t="str">
+        <v/>
+      </c>
+      <c r="L92" t="str">
+        <v/>
+      </c>
+      <c r="M92" t="str">
+        <v/>
+      </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v/>
+      </c>
+      <c r="B93" t="str">
+        <v>TOTAL INC GST</v>
+      </c>
+      <c r="C93">
+        <v>59444</v>
+      </c>
+      <c r="D93" t="str">
+        <v/>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
+      <c r="J93" t="str">
+        <v/>
+      </c>
+      <c r="K93" t="str">
+        <v/>
+      </c>
+      <c r="L93" t="str">
+        <v/>
+      </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
+      <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M84"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O93"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D17"/>
+  <cols>
+    <col min="1" max="1" width="32.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="4.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Mettro Estimating Guide &amp; Rates</v>
+      </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>GST %</v>
+      </c>
+      <c r="B3">
+        <v>0.1</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Contingency %</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Retainer / commitment discount %</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>After-hours multiplier</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Role / category</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Rate ex GST</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v>Row Types</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Strategy</v>
+      </c>
+      <c r="B9">
+        <v>270</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v>Header</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Project Management</v>
+      </c>
+      <c r="B10">
+        <v>210</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v>Item</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Design</v>
+      </c>
+      <c r="B11">
+        <v>210</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v>Spacer</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Development</v>
+      </c>
+      <c r="B12">
+        <v>230</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Integration &amp; Technical</v>
+      </c>
+      <c r="B13">
+        <v>250</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Quality Assurance</v>
+      </c>
+      <c r="B14">
+        <v>170</v>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Content Entry</v>
+      </c>
+      <c r="B15">
+        <v>170</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Standard Support</v>
+      </c>
+      <c r="B16">
+        <v>200</v>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>External Contractor</v>
+      </c>
+      <c r="B17">
+        <v>200</v>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D17"/>
   </ignoredErrors>
 </worksheet>
 </file>